--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-historique-de-la-grossesse.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-historique-de-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cette entrée permet de regrouper les observations relatives à un épisode de grossesse.</t>
+    <t>FrHistoriqueGrossesse permet de regrouper les observations relatives à un épisode de grossesse.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -491,7 +491,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l'entrée</t>
+    <t>Identifiant de l'observation</t>
   </si>
   <si>
     <t>A unique identifier assigned to this observation.</t>
@@ -573,7 +573,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>Statut de l’entrée</t>
+    <t>Statut de l'observation</t>
   </si>
   <si>
     <t>The status of the result value.</t>
